--- a/results/breakdown/2050/hydrogen peroxide production, AO, fossil hydrogen.xlsx
+++ b/results/breakdown/2050/hydrogen peroxide production, AO, fossil hydrogen.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
   <si>
     <t>target</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>'market for wastewater, average' (cubic meter, RoW, None)</t>
-  </si>
-  <si>
-    <t>'market for palladium' (kilogram, GLO, None)</t>
   </si>
   <si>
     <t>'market group for electricity, high voltage' (kilowatt hour, GLO, None)</t>
@@ -410,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -429,7 +426,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -438,7 +435,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>1.131621234083362</v>
+        <v>1.1491449273765</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -455,7 +452,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.8516485543313149</v>
+        <v>0.8627721694083842</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -472,7 +469,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.06704253347043446</v>
+        <v>0.06707546264206161</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -489,7 +486,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.003635049264385066</v>
+        <v>0.003825343943470708</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -506,7 +503,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.0001514669458100168</v>
+        <v>0.0001671627538251456</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -523,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>5.304271072744067E-06</v>
+        <v>0.0004938917251351401</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -540,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>-0.004502379199489708</v>
+        <v>8.640005529441824E-06</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -557,26 +554,9 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>-7.876337909608076E-05</v>
+        <v>0.1334745856061964</v>
       </c>
       <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
-        <v>0.1323917965961181</v>
-      </c>
-      <c r="E10">
         <v>1</v>
       </c>
     </row>

--- a/results/breakdown/2050/hydrogen peroxide production, AO, fossil hydrogen.xlsx
+++ b/results/breakdown/2050/hydrogen peroxide production, AO, fossil hydrogen.xlsx
@@ -435,7 +435,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>1.1491449273765</v>
+        <v>1.149144927376501</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -452,7 +452,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.8627721694083842</v>
+        <v>0.8627721694083846</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.003825343943470708</v>
+        <v>0.003825343943470703</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -503,7 +503,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.0001671627538251456</v>
+        <v>0.0001671627538251459</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.0004938917251351401</v>
+        <v>0.0004938917251351344</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -537,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>8.640005529441824E-06</v>
+        <v>8.640005529441858E-06</v>
       </c>
       <c r="E8">
         <v>1</v>
